--- a/tests/TestResult/Overview.xlsx
+++ b/tests/TestResult/Overview.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mithi\OneDrive\Desktop\MyProject\lni-reference-checker\tests\TestResult\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180C7223-3E27-4FCE-8BCB-3D3940BFB532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DB657D-573F-495A-BBD6-BE4C481B754E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>Filename</t>
   </si>
@@ -87,6 +87,21 @@
   </si>
   <si>
     <t>Real: Ar17 (95%), He17 (95%), Bi17 (100%). Fake: FL20 (73%), VB20 (73%). Suspicious: We23 (78%). Key mismatches: All 6 detected. Missing citations: 3 detected (Ar10, FI25, He22). Orphaned: 0. DUPLICATE DETECTION: Ar17 and He17 flagged as duplicates with badge. Verdict: FAIL.</t>
+  </si>
+  <si>
+    <t>LNI_Test_Suite_03.pdf</t>
+  </si>
+  <si>
+    <t>Mixed Real &amp; Fake References with LNI Validation - Document contains 1 real academic paper (Graves et al. 2004, already in DB) and 5 fabricated/suspicious papers. All 6 entries have incorrect LNI citation keys or formatting issues. 3 citations in text are missing from bibliography. Tests real/fake detection with DB match, cross-correlation, LNI standards compliance, and entry type classification.</t>
+  </si>
+  <si>
+    <t>Ar20, He04, Fi21, Bi21, VB20, We22, Ar10, FI25, He22</t>
+  </si>
+  <si>
+    <t>Real paper (He04) should show REAL (87% from DB). Fake papers (Ar20, Bi21, VB20, We22) should show SUSPICIOUS/FAKE. All 6 entries should show key mismatch and incomplete fields. 3 missing citations (Ar10, FI25, He22) should be flagged. 0 orphaned entries. Overall verdict should be FAIL.</t>
+  </si>
+  <si>
+    <t>Real: He04 (87% from DB). Fake: 1 confirmed fake (Bi21). Suspicious: Ar20, VB20, We22. Key mismatches: All 6 detected. Missing citations: 3 detected (Ar10, FI25, He22). Orphaned: 0. Incomplete entries: All 6 flagged. Verdict: FAIL (60/100, C+).</t>
   </si>
 </sst>
 </file>
@@ -161,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -189,6 +204,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -470,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DF3"/>
+  <dimension ref="A1:DF4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.44140625" style="1" customWidth="1"/>
@@ -546,6 +568,26 @@
         <v>11</v>
       </c>
     </row>
+    <row r="4" spans="1:110" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
